--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/3. user_area/1. language.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/3. user_area/1. language.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\3. user_area\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A8670B-374B-4651-AB47-C67F9FB460B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E508B12-F210-45C7-B1F3-75E6963238DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="table" sheetId="1" r:id="rId1"/>
@@ -358,12 +358,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
